--- a/stats for com eng/excel files/Ch4-05.xlsx
+++ b/stats for com eng/excel files/Ch4-05.xlsx
@@ -1,22 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pin/Desktop/joint-repository/stats for com eng/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pin/Desktop/joint-repository/stats for com eng/excel files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B500527-BD21-1948-8CF8-9130C925E45F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C1DCF9-644E-6C44-BC52-11BD3DF84814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="24080" windowHeight="13240" activeTab="3" xr2:uid="{C748285C-19E1-4F2D-927D-6F526C53A5E8}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="20480" windowHeight="11040" activeTab="7" xr2:uid="{C748285C-19E1-4F2D-927D-6F526C53A5E8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet1 practice" sheetId="5" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet2 practice" sheetId="6" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId5"/>
+    <sheet name="Sheet3 practice" sheetId="7" r:id="rId6"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId7"/>
+    <sheet name="Sheet4 practice" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="118">
   <si>
     <t>P(Z &gt; 1.90)</t>
   </si>
@@ -748,6 +752,212 @@
   </si>
   <si>
     <t>That means the mean of SAT score is  500 at significant level 0.01</t>
+  </si>
+  <si>
+    <t>Type I error, reject null hypothesis when sample is possible to come from null hypothesis world</t>
+  </si>
+  <si>
+    <t>Type II error, fail to reject null hypothesis even though it is impossible that sample comes from null hypothesis</t>
+  </si>
+  <si>
+    <t>mean must be 50</t>
+  </si>
+  <si>
+    <t>standard dev (sigma) = 2</t>
+  </si>
+  <si>
+    <t>significant level 0.05</t>
+  </si>
+  <si>
+    <t>n=25</t>
+  </si>
+  <si>
+    <t>mean sample = 51.3</t>
+  </si>
+  <si>
+    <t>two tails (must be exact that value)</t>
+  </si>
+  <si>
+    <t>null hyp.</t>
+  </si>
+  <si>
+    <t>mu = 50</t>
+  </si>
+  <si>
+    <t>alter</t>
+  </si>
+  <si>
+    <t>mu != 50</t>
+  </si>
+  <si>
+    <t>alpha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n </t>
+  </si>
+  <si>
+    <t>pop std</t>
+  </si>
+  <si>
+    <t>test statistics</t>
+  </si>
+  <si>
+    <t>Xbar sample mean</t>
+  </si>
+  <si>
+    <t>left critical value</t>
+  </si>
+  <si>
+    <t>right critical value</t>
+  </si>
+  <si>
+    <t>test statistics exceed critical value, reject</t>
+  </si>
+  <si>
+    <t>P value</t>
+  </si>
+  <si>
+    <t>not possible to be in null hypothesis world, reject</t>
+  </si>
+  <si>
+    <t>Because test statistics has exceeded critical value, and P value is lower than alpha, we have strong evidence to reject H null, meaning that the true mean burning rate of the rocket propulsion (given) is not 50 cm/sec</t>
+  </si>
+  <si>
+    <t>sample mean</t>
+  </si>
+  <si>
+    <t>x bar</t>
+  </si>
+  <si>
+    <t>hypothesis</t>
+  </si>
+  <si>
+    <t>sample std dev</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <r>
+      <t>t(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Symbol"/>
+        <family val="1"/>
+        <charset val="2"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> critical value</t>
+    </r>
+  </si>
+  <si>
+    <t>Reject Region (right tail)</t>
+  </si>
+  <si>
+    <t>P value &lt; alpha reject</t>
+  </si>
+  <si>
+    <t>t0 &gt; critical value reject</t>
+  </si>
+  <si>
+    <t>we have strong evidence to reject H0 (with both test statistic and P value)</t>
+  </si>
+  <si>
+    <t>meaning the mean coefficient of restitution exceeds 0.82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean </t>
+  </si>
+  <si>
+    <t>stdev sample</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">H1: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Symbol"/>
+        <family val="1"/>
+        <charset val="2"/>
+      </rPr>
+      <t>m != 500</t>
+    </r>
+  </si>
+  <si>
+    <t>two tail</t>
+  </si>
+  <si>
+    <r>
+      <t>t(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Symbol"/>
+        <family val="1"/>
+        <charset val="2"/>
+      </rPr>
+      <t>a/2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> critical value</t>
+    </r>
+  </si>
+  <si>
+    <t>t0 &lt; t(alpha/2) or t0 &gt; t(1-alpha/2) reject</t>
+  </si>
+  <si>
+    <t>We have strong evidence to not reject H0</t>
+  </si>
+  <si>
+    <t>For the total SAT score, we have strong evidence to claim that their mean is 500</t>
+  </si>
+  <si>
+    <t>t(alpha/2)</t>
+  </si>
+  <si>
+    <t>t(1-alpha/2)</t>
   </si>
 </sst>
 </file>
@@ -891,7 +1101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -945,16 +1155,25 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -978,6 +1197,18 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Radio" firstButton="1" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp10.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Radio" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp11.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Radio" checked="Checked" firstButton="1" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Radio" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Radio" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
@@ -991,11 +1222,23 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Radio" checked="Checked" firstButton="1" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Radio" firstButton="1" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Radio" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Radio" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Radio" firstButton="1" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Radio" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp9.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Radio" checked="Checked" firstButton="1" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1012,8 +1255,8 @@
         <xdr:to>
           <xdr:col>1</xdr:col>
           <xdr:colOff>965200</xdr:colOff>
-          <xdr:row>16</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>254000</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1023,7 +1266,7 @@
                   <a14:compatExt spid="_x0000_s2050"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002080000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1098,8 +1341,8 @@
         <xdr:to>
           <xdr:col>1</xdr:col>
           <xdr:colOff>939800</xdr:colOff>
-          <xdr:row>17</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>254000</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1109,7 +1352,7 @@
                   <a14:compatExt spid="_x0000_s2051"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003080000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1303,6 +1546,393 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>12700</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>25400</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>965200</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="9217" name="Option Button 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s9217"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000001240000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>Accept H0</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>12700</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>25400</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>939800</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="9218" name="Option Button 2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s9218"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002240000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>Reject H0</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1133475</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>245674</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51C2F79B-806E-9549-B205-9BB13BF9B855}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5003800" y="1797050"/>
+          <a:ext cx="1108075" cy="480624"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>47624</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>28780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1714500</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9ED0C005-0EA7-954A-A794-AA7AB9E479AA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5026024" y="3330780"/>
+          <a:ext cx="1666876" cy="253795"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>53203</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>195385</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>169911</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2386E44D-3FF3-1D4A-CB60-C16F52216C78}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="53203" y="5049941"/>
+          <a:ext cx="4921590" cy="1252041"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>465917</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>97692</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>260914</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>81986</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A3D2C4B-F4DB-C03E-9D53-3F4CBB516A9D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9250710" y="6485266"/>
+          <a:ext cx="1117600" cy="495300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>12700</xdr:colOff>
           <xdr:row>16</xdr:row>
@@ -1322,7 +1952,7 @@
                   <a14:compatExt spid="_x0000_s3073"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-0000010C0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-0000010C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1408,7 +2038,7 @@
                   <a14:compatExt spid="_x0000_s3074"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-0000020C0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-0000020C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1535,7 +2165,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -1554,13 +2184,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="4097" name="Option Button 1" hidden="1">
+            <xdr:cNvPr id="10241" name="Option Button 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4097"/>
+                  <a14:compatExt spid="_x0000_s10241"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000001100000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000001280000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1636,7 +2266,289 @@
           <xdr:col>2</xdr:col>
           <xdr:colOff>939800</xdr:colOff>
           <xdr:row>18</xdr:row>
-          <xdr:rowOff>1186</xdr:rowOff>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="10242" name="Option Button 2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s10242"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002280000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>Reject H0</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>41274</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1315507</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>130175</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F66A9FF9-F525-D34D-A8EB-34107AEC1163}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5908674" y="1898650"/>
+          <a:ext cx="1274233" cy="517525"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1790700</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>215900</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62A56F2A-01B9-214F-70D1-218FA45D2EFE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7658100" y="2463800"/>
+          <a:ext cx="4940300" cy="4356100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>12700</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>25400</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>965200</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>254000</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4097" name="Option Button 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s4097"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000001100000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>Accept H0</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>12700</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>25400</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>939800</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>254000</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1646,7 +2558,7 @@
                   <a14:compatExt spid="_x0000_s4098"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002100000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002100000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1766,6 +2678,288 @@
             </a14:hiddenFill>
           </a:ext>
         </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>12700</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>25400</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>965200</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="16385" name="Option Button 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s16385"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F521F8F-DF38-714F-883B-5D7FBD24909D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>Accept H0</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>12700</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>25400</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>939800</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>2936</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="16386" name="Option Button 2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s16386"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0091003-0CDB-6749-BC3D-AEA8D8626307}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>Reject H0</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>41274</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1315507</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>130175</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F4F72FD-3FD3-F247-B733-917DD8366ABB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5146674" y="1898650"/>
+          <a:ext cx="1274233" cy="517525"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1896532</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>193686</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>220133</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DC06E42-34D6-ACD8-A8D3-E002DCD12D2C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7010399" y="355600"/>
+          <a:ext cx="4884220" cy="2912533"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -2244,6 +3438,189 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16351B62-71D7-E346-9A14-634F4ED64921}">
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="20.6640625" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4">
+        <f>_xlfn.NORM.S.DIST(-1.9, TRUE)</f>
+        <v>2.87165598160018E-2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="4">
+        <f>1-_xlfn.NORM.S.DIST(1.9, TRUE)</f>
+        <v>2.8716559816001852E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5">
+        <f>B2+B3</f>
+        <v>5.7433119632003649E-2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4">
+        <f>_xlfn.NORM.S.DIST(-0.63, TRUE)</f>
+        <v>0.26434729211567748</v>
+      </c>
+      <c r="E7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4">
+        <f>_xlfn.NORM.S.DIST(-4.43, TRUE)</f>
+        <v>4.7116544118972307E-6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5">
+        <f>B7-B8</f>
+        <v>0.26434258046126557</v>
+      </c>
+      <c r="G9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="4">
+        <f>_xlfn.NORM.S.DIST(1.27, TRUE)</f>
+        <v>0.89795768492518091</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="4">
+        <f>_xlfn.NORM.S.DIST(-2.53, TRUE)</f>
+        <v>5.7031263329506993E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="5">
+        <f>B12-B13</f>
+        <v>0.89225455859223024</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="4">
+        <f>_xlfn.NORM.S.DIST(-0.8, TRUE)</f>
+        <v>0.21185539858339661</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="4">
+        <f>_xlfn.NORM.S.DIST(-5.6, TRUE)</f>
+        <v>1.0717590258310892E-8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="5">
+        <f>B17-B18</f>
+        <v>0.21185538786580635</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26BE2AEE-E0A8-43D1-B1BA-2DE96725CAC7}">
   <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -2367,7 +3744,7 @@
       <c r="A14" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="25">
+      <c r="B14" s="23">
         <f>2*(1-_xlfn.NORM.S.DIST(B9, TRUE))</f>
         <v>1.1540500847815327E-3</v>
       </c>
@@ -2453,7 +3830,327 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28963249-0C47-E749-90E2-4FB45BD7DFA4}">
+  <dimension ref="A1:F35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="32.6640625" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="32.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="8">
+        <v>51.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="10"/>
+    </row>
+    <row r="10" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="8">
+        <f>B5/2</f>
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="9"/>
+    </row>
+    <row r="12" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="8"/>
+    </row>
+    <row r="13" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="23">
+        <f>2*(1-_xlfn.NORM.S.DIST(B9, TRUE))</f>
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="9"/>
+      <c r="C15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" t="s">
+        <v>82</v>
+      </c>
+      <c r="E22" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C24" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" t="s">
+        <v>86</v>
+      </c>
+      <c r="E24">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C25" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" t="s">
+        <v>88</v>
+      </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C27" t="s">
+        <v>81</v>
+      </c>
+      <c r="D27" t="s">
+        <v>90</v>
+      </c>
+      <c r="E27">
+        <v>51.3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C29" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29">
+        <f>(E27-50)/(E26/SQRT(E25))</f>
+        <v>3.2499999999999929</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C30" t="s">
+        <v>91</v>
+      </c>
+      <c r="D30">
+        <f>_xlfn.NORM.S.INV(0.05/2)</f>
+        <v>-1.9599639845400538</v>
+      </c>
+      <c r="F30" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C31" t="s">
+        <v>92</v>
+      </c>
+      <c r="D31">
+        <f>_xlfn.NORM.S.INV(1-0.05/2)</f>
+        <v>1.9599639845400536</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C32" t="s">
+        <v>94</v>
+      </c>
+      <c r="D32">
+        <f>2*(1-_xlfn.NORM.S.DIST(ABS(D29),TRUE))</f>
+        <v>1.1540500847815327E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="3:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C33" t="s">
+        <v>86</v>
+      </c>
+      <c r="D33">
+        <v>0.05</v>
+      </c>
+      <c r="F33" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="35" spans="3:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C35" t="s">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="9217" r:id="rId3" name="Option Button 1">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>12700</xdr:colOff>
+                    <xdr:row>15</xdr:row>
+                    <xdr:rowOff>25400</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>965200</xdr:colOff>
+                    <xdr:row>16</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="9218" r:id="rId4" name="Option Button 2">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>12700</xdr:colOff>
+                    <xdr:row>16</xdr:row>
+                    <xdr:rowOff>25400</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>939800</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{312775D8-508D-4202-BCB1-2E0E65629357}">
   <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -2575,7 +4272,7 @@
         <f>(C3-0.82)/(C4/SQRT(C5))</f>
         <v>2.7189787825251419</v>
       </c>
-      <c r="D11" s="26" t="s">
+      <c r="D11" s="24" t="s">
         <v>66</v>
       </c>
     </row>
@@ -2590,7 +4287,7 @@
         <f>_xlfn.T.INV(1-C10, C5-1)</f>
         <v>1.7613101357748921</v>
       </c>
-      <c r="D12" s="26" t="s">
+      <c r="D12" s="24" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2598,7 +4295,7 @@
       <c r="A13" s="14">
         <v>0.80420000000000003</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="25" t="s">
         <v>17</v>
       </c>
       <c r="C13" s="19" t="s">
@@ -2612,7 +4309,7 @@
       <c r="A14" s="14">
         <v>0.873</v>
       </c>
-      <c r="B14" s="24"/>
+      <c r="B14" s="26"/>
       <c r="C14" s="15" t="s">
         <v>31</v>
       </c>
@@ -2631,7 +4328,7 @@
         <f>1-_xlfn.T.DIST(C11, C5-1, TRUE)</f>
         <v>8.3133686815108909E-3</v>
       </c>
-      <c r="D15" s="26" t="s">
+      <c r="D15" s="24" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2710,7 +4407,298 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58BE9B35-1358-9C40-83B0-9657C8855D85}">
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="20.6640625" style="14" customWidth="1"/>
+    <col min="2" max="2" width="30.6640625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="25.6640625" style="13" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" style="12" customWidth="1"/>
+    <col min="5" max="16384" width="8.6640625" style="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="14">
+        <v>0.84109999999999996</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="16">
+        <f>AVERAGE(A3:A17)</f>
+        <v>0.83723999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="14">
+        <v>0.81910000000000005</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="16">
+        <f>_xlfn.STDEV.S(A3:A17)</f>
+        <v>2.4557099642611345E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="14">
+        <v>0.81820000000000004</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="17">
+        <v>15</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="G5" s="27">
+        <f>C3</f>
+        <v>0.83723999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="14">
+        <v>0.8125</v>
+      </c>
+      <c r="C6" s="18"/>
+      <c r="E6" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="G6" s="12">
+        <f>0.82</f>
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="14">
+        <v>0.875</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="G7" s="27">
+        <f>C4</f>
+        <v>2.4557099642611345E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="14">
+        <v>0.85799999999999998</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G8" s="28">
+        <f>C5</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="14">
+        <v>0.85319999999999996</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="14">
+        <v>0.84830000000000005</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="19">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="14">
+        <v>0.8276</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="16">
+        <f>(C3-0.82)/(C4/SQRT(C5))</f>
+        <v>2.7189787825251419</v>
+      </c>
+      <c r="D11" s="24"/>
+    </row>
+    <row r="12" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="14">
+        <v>0.79830000000000001</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="C12" s="21">
+        <f>_xlfn.T.INV(1-C10, C5-1)</f>
+        <v>1.7613101357748921</v>
+      </c>
+      <c r="D12" s="24"/>
+    </row>
+    <row r="13" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="14">
+        <v>0.80420000000000003</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="14">
+        <v>0.873</v>
+      </c>
+      <c r="B14" s="26"/>
+      <c r="C14" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="14">
+        <v>0.82820000000000005</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="21">
+        <f>1-_xlfn.T.DIST(C11, C5-1, TRUE)</f>
+        <v>8.3133686815108909E-3</v>
+      </c>
+      <c r="D15" s="24"/>
+    </row>
+    <row r="16" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="14">
+        <v>0.83589999999999998</v>
+      </c>
+      <c r="C16" s="14"/>
+    </row>
+    <row r="17" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="14">
+        <v>0.86599999999999999</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="12" t="s">
+        <v>107</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B13:B14"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="10241" r:id="rId4" name="Option Button 1">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>12700</xdr:colOff>
+                    <xdr:row>16</xdr:row>
+                    <xdr:rowOff>25400</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>965200</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="10242" r:id="rId5" name="Option Button 2">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>12700</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>25400</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>939800</xdr:colOff>
+                    <xdr:row>18</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7E11E96-8D00-4531-A440-8667193B6527}">
   <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -2822,7 +4810,7 @@
     </row>
     <row r="13" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="12"/>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="25" t="s">
         <v>17</v>
       </c>
       <c r="C13" s="19" t="s">
@@ -2834,7 +4822,7 @@
     </row>
     <row r="14" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12"/>
-      <c r="B14" s="24"/>
+      <c r="B14" s="26"/>
       <c r="C14" s="15" t="s">
         <v>31</v>
       </c>
@@ -2939,4 +4927,252 @@
     </mc:Choice>
   </mc:AlternateContent>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64371C9A-A110-2B46-BDDA-E183BDED00B1}">
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="5.6640625" style="14" customWidth="1"/>
+    <col min="2" max="2" width="28.6640625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="32.6640625" style="13" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" style="12" customWidth="1"/>
+    <col min="5" max="16384" width="8.6640625" style="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="12"/>
+    </row>
+    <row r="3" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="12"/>
+      <c r="B3" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="17">
+        <v>510</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="12"/>
+      <c r="B4" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="17">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="12"/>
+      <c r="B5" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="17">
+        <v>140</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="12"/>
+      <c r="C6" s="12"/>
+    </row>
+    <row r="7" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="12"/>
+      <c r="B7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="12"/>
+      <c r="B8" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="12"/>
+      <c r="B9" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="12"/>
+      <c r="B10" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="19">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="12"/>
+      <c r="B11" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="22">
+        <f>(C3-500)/(C5/SQRT(C4))</f>
+        <v>0.30304576336566319</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="12"/>
+      <c r="B12" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" s="21">
+        <f>_xlfn.T.INV(C10/2, C4-1)</f>
+        <v>-2.8982305196774178</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="12"/>
+      <c r="B13" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="12"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="12"/>
+      <c r="B15" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="21">
+        <f>2*(1-_xlfn.T.DIST(ABS(C11), C4-1, TRUE))</f>
+        <v>0.76553202595584557</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="12"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="E16" s="12">
+        <f>_xlfn.T.INV(C10/2, C4-1)</f>
+        <v>-2.8982305196774178</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E17" s="12">
+        <f>_xlfn.T.INV(1-C10/2, C4-1)</f>
+        <v>2.8982305196774178</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="12"/>
+    </row>
+    <row r="19" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="12"/>
+      <c r="B19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C19" s="8"/>
+    </row>
+    <row r="20" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="C20" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B13:B14"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="16385" r:id="rId3" name="Option Button 1">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>12700</xdr:colOff>
+                    <xdr:row>16</xdr:row>
+                    <xdr:rowOff>25400</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>965200</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="16386" r:id="rId4" name="Option Button 2">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>12700</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>25400</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>939800</xdr:colOff>
+                    <xdr:row>18</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
 </file>